--- a/Unit Testing Generates/FCS/WOD_2__Claim__c/unitTest_WOD_2__Claim__c.xlsx
+++ b/Unit Testing Generates/FCS/WOD_2__Claim__c/unitTest_WOD_2__Claim__c.xlsx
@@ -441,13 +441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -529,7 +529,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_1_001</t>
+          <t>POS_Mc Pc Pre Auth Comments Mandatory_001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_1 passes with valid business rule data</t>
+          <t>Verify Mc Pc Pre Auth Comments Mandatory passes with valid business rule data</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ValidationRule_1</t>
+          <t>Mc Pc Pre Auth Comments Mandatory</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_1_001</t>
+          <t>EDGE_Mc Pc Pre Auth Comments Mandatory_001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_1 handles boundary conditions correctly</t>
+          <t>Verify Mc Pc Pre Auth Comments Mandatory handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ValidationRule_1</t>
+          <t>Mc Pc Pre Auth Comments Mandatory</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_2_001</t>
+          <t>POS_Mc Pc Pre Auth Reason Mandatory_001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_2 passes with valid business rule data</t>
+          <t>Verify Mc Pc Pre Auth Reason Mandatory passes with valid business rule data</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ValidationRule_2</t>
+          <t>Mc Pc Pre Auth Reason Mandatory</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -730,7 +730,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_2_001</t>
+          <t>EDGE_Mc Pc Pre Auth Reason Mandatory_001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_2 handles boundary conditions correctly</t>
+          <t>Verify Mc Pc Pre Auth Reason Mandatory handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ValidationRule_2</t>
+          <t>Mc Pc Pre Auth Reason Mandatory</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_3_001</t>
+          <t>POS_Mc Purchasedate Less Repairdate Failure_001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_3 passes with valid business rule data</t>
+          <t>Verify Mc Purchasedate Less Repairdate Failure passes with valid business rule data</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ValidationRule_3</t>
+          <t>Mc Purchasedate Less Repairdate Failure</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_3_001</t>
+          <t>EDGE_Mc Purchasedate Less Repairdate Failure_001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_3 handles boundary conditions correctly</t>
+          <t>Verify Mc Purchasedate Less Repairdate Failure handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ValidationRule_3</t>
+          <t>Mc Purchasedate Less Repairdate Failure</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_4_001</t>
+          <t>POS_Osd Receivedate Less Today_001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_4 passes with valid business rule data</t>
+          <t>Verify Osd Receivedate Less Today passes with valid business rule data</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ValidationRule_4</t>
+          <t>Osd Receivedate Less Today</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -998,7 +998,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_4_001</t>
+          <t>EDGE_Osd Receivedate Less Today_001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_4 handles boundary conditions correctly</t>
+          <t>Verify Osd Receivedate Less Today handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ValidationRule_4</t>
+          <t>Osd Receivedate Less Today</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_5_001</t>
+          <t>POS_Pc Part Sno Mandatory_001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_5 passes with valid business rule data</t>
+          <t>Verify Pc Part Sno Mandatory passes with valid business rule data</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ValidationRule_5</t>
+          <t>Pc Part Sno Mandatory</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_5_001</t>
+          <t>EDGE_Pc Part Sno Mandatory_001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_5 handles boundary conditions correctly</t>
+          <t>Verify Pc Part Sno Mandatory handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ValidationRule_5</t>
+          <t>Pc Part Sno Mandatory</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_6_001</t>
+          <t>POS_Preauth Expiry Date Check_001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_6 passes with valid business rule data</t>
+          <t>Verify Preauth Expiry Date Check passes with valid business rule data</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ValidationRule_6</t>
+          <t>Preauth Expiry Date Check</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_6_001</t>
+          <t>EDGE_Preauth Expiry Date Check_001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_6 handles boundary conditions correctly</t>
+          <t>Verify Preauth Expiry Date Check handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ValidationRule_6</t>
+          <t>Preauth Expiry Date Check</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_7_001</t>
+          <t>POS_Preauth Fulfilled Check_001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_7 passes with valid business rule data</t>
+          <t>Verify Preauth Fulfilled Check passes with valid business rule data</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ValidationRule_7</t>
+          <t>Preauth Fulfilled Check</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1400,7 +1400,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_7_001</t>
+          <t>EDGE_Preauth Fulfilled Check_001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_7 handles boundary conditions correctly</t>
+          <t>Verify Preauth Fulfilled Check handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ValidationRule_7</t>
+          <t>Preauth Fulfilled Check</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1467,7 +1467,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_8_001</t>
+          <t>POS_Claim Is Locked_001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_8 passes with valid business rule data</t>
+          <t>Verify Claim Is Locked passes with valid business rule data</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ValidationRule_8</t>
+          <t>Claim Is Locked</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_8_001</t>
+          <t>EDGE_Claim Is Locked_001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_8 handles boundary conditions correctly</t>
+          <t>Verify Claim Is Locked handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ValidationRule_8</t>
+          <t>Claim Is Locked</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_9_001</t>
+          <t>POS_Failure Date Validation Rule_001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_9 passes with valid business rule data</t>
+          <t>Verify Failure Date Validation Rule passes with valid business rule data</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ValidationRule_9</t>
+          <t>Failure Date Validation Rule</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_9_001</t>
+          <t>EDGE_Failure Date Validation Rule_001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_9 handles boundary conditions correctly</t>
+          <t>Verify Failure Date Validation Rule handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ValidationRule_9</t>
+          <t>Failure Date Validation Rule</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1735,7 +1735,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_10_001</t>
+          <t>POS_Goodwill Type Is Missing_001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_10 passes with valid business rule data</t>
+          <t>Verify Goodwill Type Is Missing passes with valid business rule data</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ValidationRule_10</t>
+          <t>Goodwill Type Is Missing</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1802,7 +1802,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_10_001</t>
+          <t>EDGE_Goodwill Type Is Missing_001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_10 handles boundary conditions correctly</t>
+          <t>Verify Goodwill Type Is Missing handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ValidationRule_10</t>
+          <t>Goodwill Type Is Missing</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1869,7 +1869,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_11_001</t>
+          <t>POS_Kbt Mc Pc Causal Mandatory_001</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_11 passes with valid business rule data</t>
+          <t>Verify Kbt Mc Pc Causal Mandatory passes with valid business rule data</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ValidationRule_11</t>
+          <t>Kbt Mc Pc Causal Mandatory</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_11_001</t>
+          <t>EDGE_Kbt Mc Pc Causal Mandatory_001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_11 handles boundary conditions correctly</t>
+          <t>Verify Kbt Mc Pc Causal Mandatory handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ValidationRule_11</t>
+          <t>Kbt Mc Pc Causal Mandatory</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_12_001</t>
+          <t>POS_Kbt Mc Pc Inventory Mandatory_001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_12 passes with valid business rule data</t>
+          <t>Verify Kbt Mc Pc Inventory Mandatory passes with valid business rule data</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ValidationRule_12</t>
+          <t>Kbt Mc Pc Inventory Mandatory</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2070,7 +2070,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_12_001</t>
+          <t>EDGE_Kbt Mc Pc Inventory Mandatory_001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_12 handles boundary conditions correctly</t>
+          <t>Verify Kbt Mc Pc Inventory Mandatory handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ValidationRule_12</t>
+          <t>Kbt Mc Pc Inventory Mandatory</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2137,7 +2137,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_13_001</t>
+          <t>POS_Incomplete Mandotory Fields_001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_13 passes with valid business rule data</t>
+          <t>Verify Incomplete Mandotory Fields passes with valid business rule data</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ValidationRule_13</t>
+          <t>Incomplete Mandotory Fields</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2204,7 +2204,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_13_001</t>
+          <t>EDGE_Incomplete Mandotory Fields_001</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_13 handles boundary conditions correctly</t>
+          <t>Verify Incomplete Mandotory Fields handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ValidationRule_13</t>
+          <t>Incomplete Mandotory Fields</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2271,7 +2271,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_14_001</t>
+          <t>POS_Kbt Pc Part Mandatory_001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_14 passes with valid business rule data</t>
+          <t>Verify Kbt Pc Part Mandatory passes with valid business rule data</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ValidationRule_14</t>
+          <t>Kbt Pc Part Mandatory</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2338,7 +2338,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_14_001</t>
+          <t>EDGE_Kbt Pc Part Mandatory_001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_14 handles boundary conditions correctly</t>
+          <t>Verify Kbt Pc Part Mandatory handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ValidationRule_14</t>
+          <t>Kbt Pc Part Mandatory</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2405,7 +2405,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_15_001</t>
+          <t>POS_Kbt Pc Purchasedate Mandatory_001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_15 passes with valid business rule data</t>
+          <t>Verify Kbt Pc Purchasedate Mandatory passes with valid business rule data</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ValidationRule_15</t>
+          <t>Kbt Pc Purchasedate Mandatory</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2472,7 +2472,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_15_001</t>
+          <t>EDGE_Kbt Pc Purchasedate Mandatory_001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_15 handles boundary conditions correctly</t>
+          <t>Verify Kbt Pc Purchasedate Mandatory handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ValidationRule_15</t>
+          <t>Kbt Pc Purchasedate Mandatory</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_16_001</t>
+          <t>POS_Mc Pc Causal Claim Template Mandatory_001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_16 passes with valid business rule data</t>
+          <t>Verify Mc Pc Causal Claim Template Mandatory passes with valid business rule data</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ValidationRule_16</t>
+          <t>Mc Pc Causal Claim Template Mandatory</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2606,7 +2606,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_16_001</t>
+          <t>EDGE_Mc Pc Causal Claim Template Mandatory_001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_16 handles boundary conditions correctly</t>
+          <t>Verify Mc Pc Causal Claim Template Mandatory handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ValidationRule_16</t>
+          <t>Mc Pc Causal Claim Template Mandatory</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2673,7 +2673,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_17_001</t>
+          <t>POS_First Usedate Mandatory_001</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_17 passes with valid business rule data</t>
+          <t>Verify First Usedate Mandatory passes with valid business rule data</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ValidationRule_17</t>
+          <t>First Usedate Mandatory</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2740,7 +2740,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_17_001</t>
+          <t>EDGE_First Usedate Mandatory_001</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_17 handles boundary conditions correctly</t>
+          <t>Verify First Usedate Mandatory handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ValidationRule_17</t>
+          <t>First Usedate Mandatory</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2807,7 +2807,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_18_001</t>
+          <t>POS_Kbt Hinposeriescode Mandatory_001</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_18 passes with valid business rule data</t>
+          <t>Verify Kbt Hinposeriescode Mandatory passes with valid business rule data</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ValidationRule_18</t>
+          <t>Kbt Hinposeriescode Mandatory</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2874,7 +2874,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_18_001</t>
+          <t>EDGE_Kbt Hinposeriescode Mandatory_001</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2884,12 +2884,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_18 handles boundary conditions correctly</t>
+          <t>Verify Kbt Hinposeriescode Mandatory handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ValidationRule_18</t>
+          <t>Kbt Hinposeriescode Mandatory</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_19_001</t>
+          <t>POS_Shippingcompany And Ref Num Mandatory_001</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_19 passes with valid business rule data</t>
+          <t>Verify Shippingcompany And Ref Num Mandatory passes with valid business rule data</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ValidationRule_19</t>
+          <t>Shippingcompany And Ref Num Mandatory</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3008,7 +3008,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_19_001</t>
+          <t>EDGE_Shippingcompany And Ref Num Mandatory_001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_19 handles boundary conditions correctly</t>
+          <t>Verify Shippingcompany And Ref Num Mandatory handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ValidationRule_19</t>
+          <t>Shippingcompany And Ref Num Mandatory</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3075,22 +3075,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_20_001</t>
+          <t>EDL_Mc Pc Pre Auth Comments Mandatory_POS_001</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_20 passes with valid business rule data</t>
+          <t>Load valid data that should pass Mc Pc Pre Auth Comments Mandatory validation</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ValidationRule_20</t>
+          <t>Mc Pc Pre Auth Comments Mandatory</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3142,22 +3142,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_20_001</t>
+          <t>EDL_Mc Pc Pre Auth Comments Mandatory_NEG_001</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_20 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Mc Pc Pre Auth Comments Mandatory validation</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ValidationRule_20</t>
+          <t>Mc Pc Pre Auth Comments Mandatory</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3209,22 +3209,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_21_001</t>
+          <t>EDL_Mc Pc Pre Auth Reason Mandatory_POS_002</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_21 passes with valid business rule data</t>
+          <t>Load valid data that should pass Mc Pc Pre Auth Reason Mandatory validation</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ValidationRule_21</t>
+          <t>Mc Pc Pre Auth Reason Mandatory</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3276,22 +3276,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_21_001</t>
+          <t>EDL_Mc Pc Pre Auth Reason Mandatory_NEG_002</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_21 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Mc Pc Pre Auth Reason Mandatory validation</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ValidationRule_21</t>
+          <t>Mc Pc Pre Auth Reason Mandatory</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3343,22 +3343,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_22_001</t>
+          <t>EDL_Mc Purchasedate Less Repairdate Failure_POS_003</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_22 passes with valid business rule data</t>
+          <t>Load valid data that should pass Mc Purchasedate Less Repairdate Failure validation</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ValidationRule_22</t>
+          <t>Mc Purchasedate Less Repairdate Failure</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3410,22 +3410,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_22_001</t>
+          <t>EDL_Mc Purchasedate Less Repairdate Failure_NEG_003</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_22 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Mc Purchasedate Less Repairdate Failure validation</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ValidationRule_22</t>
+          <t>Mc Purchasedate Less Repairdate Failure</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3477,22 +3477,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_23_001</t>
+          <t>EDL_Osd Receivedate Less Today_POS_004</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_23 passes with valid business rule data</t>
+          <t>Load valid data that should pass Osd Receivedate Less Today validation</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ValidationRule_23</t>
+          <t>Osd Receivedate Less Today</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3544,22 +3544,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_23_001</t>
+          <t>EDL_Osd Receivedate Less Today_NEG_004</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_23 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Osd Receivedate Less Today validation</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ValidationRule_23</t>
+          <t>Osd Receivedate Less Today</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3611,22 +3611,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_24_001</t>
+          <t>EDL_Pc Part Sno Mandatory_POS_005</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_24 passes with valid business rule data</t>
+          <t>Load valid data that should pass Pc Part Sno Mandatory validation</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ValidationRule_24</t>
+          <t>Pc Part Sno Mandatory</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3678,22 +3678,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_24_001</t>
+          <t>EDL_Pc Part Sno Mandatory_NEG_005</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_24 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Pc Part Sno Mandatory validation</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ValidationRule_24</t>
+          <t>Pc Part Sno Mandatory</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3745,22 +3745,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_25_001</t>
+          <t>EDL_Preauth Expiry Date Check_POS_006</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_25 passes with valid business rule data</t>
+          <t>Load valid data that should pass Preauth Expiry Date Check validation</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ValidationRule_25</t>
+          <t>Preauth Expiry Date Check</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3812,22 +3812,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_25_001</t>
+          <t>EDL_Preauth Expiry Date Check_NEG_006</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_25 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Preauth Expiry Date Check validation</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ValidationRule_25</t>
+          <t>Preauth Expiry Date Check</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3879,22 +3879,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_26_001</t>
+          <t>EDL_Preauth Fulfilled Check_POS_007</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_26 passes with valid business rule data</t>
+          <t>Load valid data that should pass Preauth Fulfilled Check validation</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ValidationRule_26</t>
+          <t>Preauth Fulfilled Check</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3946,22 +3946,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_26_001</t>
+          <t>EDL_Preauth Fulfilled Check_NEG_007</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_26 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Preauth Fulfilled Check validation</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ValidationRule_26</t>
+          <t>Preauth Fulfilled Check</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4013,22 +4013,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_27_001</t>
+          <t>EDL_Claim Is Locked_POS_008</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_27 passes with valid business rule data</t>
+          <t>Load valid data that should pass Claim Is Locked validation</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ValidationRule_27</t>
+          <t>Claim Is Locked</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4080,22 +4080,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_27_001</t>
+          <t>EDL_Claim Is Locked_NEG_008</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_27 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Claim Is Locked validation</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ValidationRule_27</t>
+          <t>Claim Is Locked</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4147,22 +4147,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_28_001</t>
+          <t>EDL_Failure Date Validation Rule_POS_009</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_28 passes with valid business rule data</t>
+          <t>Load valid data that should pass Failure Date Validation Rule validation</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ValidationRule_28</t>
+          <t>Failure Date Validation Rule</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4214,22 +4214,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_28_001</t>
+          <t>EDL_Failure Date Validation Rule_NEG_009</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_28 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Failure Date Validation Rule validation</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ValidationRule_28</t>
+          <t>Failure Date Validation Rule</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4281,22 +4281,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_29_001</t>
+          <t>EDL_Goodwill Type Is Missing_POS_010</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_29 passes with valid business rule data</t>
+          <t>Load valid data that should pass Goodwill Type Is Missing validation</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ValidationRule_29</t>
+          <t>Goodwill Type Is Missing</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4348,22 +4348,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_29_001</t>
+          <t>EDL_Goodwill Type Is Missing_NEG_010</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_29 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Goodwill Type Is Missing validation</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ValidationRule_29</t>
+          <t>Goodwill Type Is Missing</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4415,22 +4415,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_30_001</t>
+          <t>EDL_Kbt Mc Pc Causal Mandatory_POS_011</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_30 passes with valid business rule data</t>
+          <t>Load valid data that should pass Kbt Mc Pc Causal Mandatory validation</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ValidationRule_30</t>
+          <t>Kbt Mc Pc Causal Mandatory</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4482,22 +4482,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_30_001</t>
+          <t>EDL_Kbt Mc Pc Causal Mandatory_NEG_011</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_30 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Kbt Mc Pc Causal Mandatory validation</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ValidationRule_30</t>
+          <t>Kbt Mc Pc Causal Mandatory</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4549,22 +4549,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_31_001</t>
+          <t>EDL_Kbt Mc Pc Inventory Mandatory_POS_012</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_31 passes with valid business rule data</t>
+          <t>Load valid data that should pass Kbt Mc Pc Inventory Mandatory validation</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ValidationRule_31</t>
+          <t>Kbt Mc Pc Inventory Mandatory</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4616,22 +4616,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_31_001</t>
+          <t>EDL_Kbt Mc Pc Inventory Mandatory_NEG_012</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_31 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Kbt Mc Pc Inventory Mandatory validation</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ValidationRule_31</t>
+          <t>Kbt Mc Pc Inventory Mandatory</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4683,22 +4683,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_32_001</t>
+          <t>EDL_Incomplete Mandotory Fields_POS_013</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_32 passes with valid business rule data</t>
+          <t>Load valid data that should pass Incomplete Mandotory Fields validation</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ValidationRule_32</t>
+          <t>Incomplete Mandotory Fields</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4750,22 +4750,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_32_001</t>
+          <t>EDL_Incomplete Mandotory Fields_NEG_013</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_32 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Incomplete Mandotory Fields validation</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ValidationRule_32</t>
+          <t>Incomplete Mandotory Fields</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4817,22 +4817,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_33_001</t>
+          <t>EDL_Kbt Pc Part Mandatory_POS_014</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_33 passes with valid business rule data</t>
+          <t>Load valid data that should pass Kbt Pc Part Mandatory validation</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ValidationRule_33</t>
+          <t>Kbt Pc Part Mandatory</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4884,22 +4884,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_33_001</t>
+          <t>EDL_Kbt Pc Part Mandatory_NEG_014</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_33 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Kbt Pc Part Mandatory validation</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ValidationRule_33</t>
+          <t>Kbt Pc Part Mandatory</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4951,22 +4951,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_34_001</t>
+          <t>EDL_Kbt Pc Purchasedate Mandatory_POS_015</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_34 passes with valid business rule data</t>
+          <t>Load valid data that should pass Kbt Pc Purchasedate Mandatory validation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ValidationRule_34</t>
+          <t>Kbt Pc Purchasedate Mandatory</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5018,22 +5018,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_34_001</t>
+          <t>EDL_Kbt Pc Purchasedate Mandatory_NEG_015</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_34 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Kbt Pc Purchasedate Mandatory validation</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ValidationRule_34</t>
+          <t>Kbt Pc Purchasedate Mandatory</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5085,22 +5085,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_35_001</t>
+          <t>EDL_Mc Pc Causal Claim Template Mandatory_POS_016</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_35 passes with valid business rule data</t>
+          <t>Load valid data that should pass Mc Pc Causal Claim Template Mandatory validation</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ValidationRule_35</t>
+          <t>Mc Pc Causal Claim Template Mandatory</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5152,22 +5152,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_35_001</t>
+          <t>EDL_Mc Pc Causal Claim Template Mandatory_NEG_016</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_35 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Mc Pc Causal Claim Template Mandatory validation</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ValidationRule_35</t>
+          <t>Mc Pc Causal Claim Template Mandatory</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5219,22 +5219,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_36_001</t>
+          <t>EDL_First Usedate Mandatory_POS_017</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_36 passes with valid business rule data</t>
+          <t>Load valid data that should pass First Usedate Mandatory validation</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ValidationRule_36</t>
+          <t>First Usedate Mandatory</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5286,22 +5286,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_36_001</t>
+          <t>EDL_First Usedate Mandatory_NEG_017</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_36 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail First Usedate Mandatory validation</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ValidationRule_36</t>
+          <t>First Usedate Mandatory</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5353,22 +5353,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_37_001</t>
+          <t>EDL_Kbt Hinposeriescode Mandatory_POS_018</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_37 passes with valid business rule data</t>
+          <t>Load valid data that should pass Kbt Hinposeriescode Mandatory validation</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ValidationRule_37</t>
+          <t>Kbt Hinposeriescode Mandatory</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5420,22 +5420,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_37_001</t>
+          <t>EDL_Kbt Hinposeriescode Mandatory_NEG_018</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_37 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Kbt Hinposeriescode Mandatory validation</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ValidationRule_37</t>
+          <t>Kbt Hinposeriescode Mandatory</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5487,22 +5487,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>POS_ValidationRule_38_001</t>
+          <t>EDL_Shippingcompany And Ref Num Mandatory_POS_019</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Positive Validation</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_38 passes with valid business rule data</t>
+          <t>Load valid data that should pass Shippingcompany And Ref Num Mandatory validation</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ValidationRule_38</t>
+          <t>Shippingcompany And Ref Num Mandatory</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5554,22 +5554,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EDGE_ValidationRule_38_001</t>
+          <t>EDL_Shippingcompany And Ref Num Mandatory_NEG_019</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Edge Case Testing</t>
+          <t>Enhanced Data Loading</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Verify ValidationRule_38 handles boundary conditions correctly</t>
+          <t>Attempt to load invalid data that should fail Shippingcompany And Ref Num Mandatory validation</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ValidationRule_38</t>
+          <t>Shippingcompany And Ref Num Mandatory</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DEPENDS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5613,2686 +5613,6 @@
         </is>
       </c>
       <c r="M77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_1_POS_001</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_1 validation</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>ValidationRule_1</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_1_NEG_001</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_1 validation</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>ValidationRule_1</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_2_POS_002</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_2 validation</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>ValidationRule_2</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_2_NEG_002</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_2 validation</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>ValidationRule_2</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_3_POS_003</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_3 validation</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>ValidationRule_3</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_3_NEG_003</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_3 validation</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>ValidationRule_3</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_4_POS_004</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_4 validation</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>ValidationRule_4</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_4_NEG_004</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_4 validation</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>ValidationRule_4</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_5_POS_005</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_5 validation</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>ValidationRule_5</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_5_NEG_005</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_5 validation</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>ValidationRule_5</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_6_POS_006</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_6 validation</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>ValidationRule_6</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_6_NEG_006</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_6 validation</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>ValidationRule_6</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_7_POS_007</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_7 validation</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>ValidationRule_7</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_7_NEG_007</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_7 validation</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>ValidationRule_7</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_8_POS_008</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_8 validation</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>ValidationRule_8</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_8_NEG_008</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_8 validation</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>ValidationRule_8</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_9_POS_009</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_9 validation</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>ValidationRule_9</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_9_NEG_009</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_9 validation</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>ValidationRule_9</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_10_POS_010</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_10 validation</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>ValidationRule_10</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_10_NEG_010</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_10 validation</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>ValidationRule_10</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_11_POS_011</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_11 validation</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>ValidationRule_11</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_11_NEG_011</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_11 validation</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>ValidationRule_11</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_12_POS_012</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_12 validation</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>ValidationRule_12</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_12_NEG_012</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_12 validation</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>ValidationRule_12</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_13_POS_013</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_13 validation</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>ValidationRule_13</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_13_NEG_013</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_13 validation</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>ValidationRule_13</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_14_POS_014</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_14 validation</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>ValidationRule_14</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_14_NEG_014</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_14 validation</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>ValidationRule_14</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_15_POS_015</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_15 validation</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>ValidationRule_15</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_15_NEG_015</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_15 validation</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>ValidationRule_15</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_16_POS_016</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_16 validation</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>ValidationRule_16</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_16_NEG_016</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_16 validation</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>ValidationRule_16</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_17_POS_017</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_17 validation</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>ValidationRule_17</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_17_NEG_017</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_17 validation</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>ValidationRule_17</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_18_POS_018</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_18 validation</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>ValidationRule_18</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_18_NEG_018</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_18 validation</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>ValidationRule_18</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_19_POS_019</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_19 validation</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>ValidationRule_19</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_19_NEG_019</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_19 validation</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>ValidationRule_19</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_20_POS_020</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Load valid data that should pass ValidationRule_20 validation</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>ValidationRule_20</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>EDL_ValidationRule_20_NEG_020</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Enhanced Data Loading</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail ValidationRule_20 validation</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>ValidationRule_20</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8309,10 +5629,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
@@ -8349,7 +5669,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ValidationRule_1</t>
+          <t>Mc Pc Pre Auth Comments Mandatory</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8364,7 +5684,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WOD_2__Pre_Authorization_Comments__c, Part, WOD_2__Claim_Type__c, WOD_2__DisableSkipTriggerNValidation, Permission, WOD_2__Is_Pre_Authorization_Required__c, Machine, WOD_2__SkipTriggerNValidations</t>
+          <t>Machine, Permission, Part, WOD_2__SkipTriggerNValidations, WOD_2__Pre_Authorization_Comments__c, WOD_2__DisableSkipTriggerNValidation, WOD_2__Is_Pre_Authorization_Required__c, WOD_2__Claim_Type__c</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8376,7 +5696,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ValidationRule_2</t>
+          <t>Mc Pc Pre Auth Reason Mandatory</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8389,7 +5709,11 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -8399,7 +5723,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ValidationRule_3</t>
+          <t>Mc Purchasedate Less Repairdate Failure</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8426,7 +5750,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ValidationRule_4</t>
+          <t>Osd Receivedate Less Today</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8439,7 +5763,11 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -8449,7 +5777,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ValidationRule_5</t>
+          <t>Pc Part Sno Mandatory</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8459,12 +5787,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>WOD_2__Is_Serialized__c, Permission, Part, WOD_2__SkipTriggerNValidations, WOD_2__Part_Serial_Number__c, WOD_2__DisableSkipTriggerNValidation, WOD_2__PartNumber_P2__r, WOD_2__Track_Type__c, Serialized, WOD_2__Claim_Type__c, WOD_2__Part__r</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -8476,7 +5804,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ValidationRule_6</t>
+          <t>Preauth Expiry Date Check</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8489,7 +5817,11 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -8499,7 +5831,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ValidationRule_7</t>
+          <t>Preauth Fulfilled Check</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8526,7 +5858,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ValidationRule_8</t>
+          <t>Claim Is Locked</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8539,7 +5871,11 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -8549,7 +5885,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ValidationRule_9</t>
+          <t>Failure Date Validation Rule</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8559,12 +5895,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Part, WOD_2__Claim_Type__c, WOD_2__PartNumber_P2__r, WOD_2__DisableSkipTriggerNValidation, Serialized, Permission, WOD_2__Part__r, WOD_2__Part_Serial_Number__c, WOD_2__Is_Serialized__c, WOD_2__Track_Type__c, WOD_2__SkipTriggerNValidations</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8576,7 +5912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ValidationRule_10</t>
+          <t>Goodwill Type Is Missing</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8589,7 +5925,11 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -8599,7 +5939,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ValidationRule_11</t>
+          <t>Kbt Mc Pc Causal Mandatory</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8609,12 +5949,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>Claim, Modification, Machine, WOD_2__Claim_Status__c, RBOX, Part, Initial, Draft, Template, Field, WOD_2__Causal_Part_Number__c, WOD_2__Claim_Type__c, KBT_Claim_Source_System__c</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8626,7 +5966,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ValidationRule_12</t>
+          <t>Kbt Mc Pc Inventory Mandatory</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8636,10 +5976,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>WOD_2__Inventory__c, WOD_2__Claim_Status__c, Machine, OEM, Part, Initial, Draft, machine, on, WOD_2__Host_NonHost__c, WOD_2__Claim_Type__c, Installed</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -8649,7 +5993,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ValidationRule_13</t>
+          <t>Incomplete Mandotory Fields</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8659,12 +6003,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>null, WOD_2__Account__c, Claim, Template, WOD_2__Date_Of_Repair__c, WOD_2__Claim_Type__c, WOD_2__Date_Of_Failure__c</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -8676,7 +6020,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ValidationRule_14</t>
+          <t>Kbt Pc Part Mandatory</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8686,10 +6030,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>WOD_2__Part__c, WOD_2__Claim_Status__c, RBOX, Part, Initial, Draft, WOD_2__Claim_Type__c, KBT_Claim_Source_System__c</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -8699,7 +6047,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ValidationRule_15</t>
+          <t>Kbt Pc Purchasedate Mandatory</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8709,12 +6057,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>WOD_2__Claim_Status__c, RBOX, Part, Initial, WOD_2__Date_Of_Purchase__c, Draft, WOD_2__Claim_Type__c, KBT_Claim_Source_System__c</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -8726,7 +6074,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ValidationRule_16</t>
+          <t>Mc Pc Causal Claim Template Mandatory</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8736,10 +6084,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Claim, Permission, WOD_2__SkipTriggerNValidations, WOD_2__DisableSkipTriggerNValidation, Template, WOD_2__CausalPartNumber_P2__c, WOD_2__Causal_Part_Number__c, WOD_2__Claim_Type__c</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -8749,7 +6101,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ValidationRule_17</t>
+          <t>First Usedate Mandatory</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8764,7 +6116,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>KBT_FirstUseDate__c, KBT_Inventory_Type__c, Retail</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8776,7 +6128,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ValidationRule_18</t>
+          <t>Kbt Hinposeriescode Mandatory</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8786,10 +6138,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WOD_2__Parent_Product__c, KBT_Reference_tracking_number__c, KBT_Shipping_Company__c, WOD_2__Item__c, WOD_2__Parent_Product__r, WOD_2__Item__r, KBT_HinpoSeriesCode__c, WOD_2__Inventory__r</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -8799,7 +6155,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ValidationRule_19</t>
+          <t>Shippingcompany And Ref Num Mandatory</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8809,488 +6165,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>KBT_Reference_tracking_number__c, KBT_Shipping_Company__c, WOD_2__Claim_Status__c, Initial, KBT_Hinpo_Code__c, Draft</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ValidationRule_20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ValidationRule_21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Initial, Field, Part, WOD_2__Claim_Status__c, WOD_2__Claim_Type__c, Modification, Draft, Claim, Machine, KBT_Claim_Source_System__c, Template, RBOX, WOD_2__Causal_Part_Number__c</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ValidationRule_22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ValidationRule_23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Initial, machine, Part, WOD_2__Claim_Status__c, WOD_2__Inventory__c, WOD_2__Claim_Type__c, Draft, Installed, OEM, Machine, on, WOD_2__Host_NonHost__c</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ValidationRule_24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ValidationRule_25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>WOD_2__Account__c, null, WOD_2__Claim_Type__c, WOD_2__Date_Of_Repair__c, Claim, WOD_2__Date_Of_Failure__c, Template</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ValidationRule_26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ValidationRule_27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Initial, Part, WOD_2__Claim_Status__c, WOD_2__Claim_Type__c, Draft, KBT_Claim_Source_System__c, RBOX, WOD_2__Part__c</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ValidationRule_28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ValidationRule_29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Initial, Part, WOD_2__Claim_Status__c, WOD_2__Claim_Type__c, Draft, WOD_2__Date_Of_Purchase__c, KBT_Claim_Source_System__c, RBOX</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>ValidationRule_30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ValidationRule_31</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>WOD_2__Claim_Type__c, WOD_2__DisableSkipTriggerNValidation, Permission, Claim, Template, WOD_2__SkipTriggerNValidations, WOD_2__CausalPartNumber_P2__c, WOD_2__Causal_Part_Number__c</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>ValidationRule_32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ValidationRule_33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Retail, KBT_FirstUseDate__c, KBT_Inventory_Type__c</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ValidationRule_34</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ValidationRule_35</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>WOD_2__Parent_Product__c, KBT_Reference_tracking_number__c, WOD_2__Item__r, KBT_Shipping_Company__c, WOD_2__Item__c, KBT_HinpoSeriesCode__c, WOD_2__Parent_Product__r, WOD_2__Inventory__r</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ValidationRule_36</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ValidationRule_37</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Initial, KBT_Hinpo_Code__c, KBT_Reference_tracking_number__c, WOD_2__Claim_Status__c, KBT_Shipping_Company__c, Draft</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ValidationRule_38</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>formula_validation</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
         <is>
           <t>General Business Rule</t>
         </is>
@@ -9391,7 +6274,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9408,7 +6291,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9476,7 +6359,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9527,7 +6410,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9573,7 +6456,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>116</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">

--- a/Unit Testing Generates/FCS/WOD_2__Claim__c/unitTest_WOD_2__Claim__c.xlsx
+++ b/Unit Testing Generates/FCS/WOD_2__Claim__c/unitTest_WOD_2__Claim__c.xlsx
@@ -441,13 +441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -529,7 +529,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POS_Mc Pc Pre Auth Comments Mandatory_001</t>
+          <t>POS_ValidationRule_1_001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Verify Mc Pc Pre Auth Comments Mandatory passes with valid business rule data</t>
+          <t>Verify ValidationRule_1 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mc Pc Pre Auth Comments Mandatory</t>
+          <t>ValidationRule_1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EDGE_Mc Pc Pre Auth Comments Mandatory_001</t>
+          <t>EDGE_ValidationRule_1_001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Verify Mc Pc Pre Auth Comments Mandatory handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_1 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mc Pc Pre Auth Comments Mandatory</t>
+          <t>ValidationRule_1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>POS_Mc Pc Pre Auth Reason Mandatory_001</t>
+          <t>POS_ValidationRule_2_001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Verify Mc Pc Pre Auth Reason Mandatory passes with valid business rule data</t>
+          <t>Verify ValidationRule_2 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mc Pc Pre Auth Reason Mandatory</t>
+          <t>ValidationRule_2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -730,7 +730,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EDGE_Mc Pc Pre Auth Reason Mandatory_001</t>
+          <t>EDGE_ValidationRule_2_001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Verify Mc Pc Pre Auth Reason Mandatory handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_2 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mc Pc Pre Auth Reason Mandatory</t>
+          <t>ValidationRule_2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>POS_Mc Purchasedate Less Repairdate Failure_001</t>
+          <t>POS_ValidationRule_3_001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Verify Mc Purchasedate Less Repairdate Failure passes with valid business rule data</t>
+          <t>Verify ValidationRule_3 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mc Purchasedate Less Repairdate Failure</t>
+          <t>ValidationRule_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EDGE_Mc Purchasedate Less Repairdate Failure_001</t>
+          <t>EDGE_ValidationRule_3_001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Verify Mc Purchasedate Less Repairdate Failure handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_3 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mc Purchasedate Less Repairdate Failure</t>
+          <t>ValidationRule_3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POS_Osd Receivedate Less Today_001</t>
+          <t>POS_ValidationRule_4_001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Verify Osd Receivedate Less Today passes with valid business rule data</t>
+          <t>Verify ValidationRule_4 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Osd Receivedate Less Today</t>
+          <t>ValidationRule_4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -998,7 +998,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EDGE_Osd Receivedate Less Today_001</t>
+          <t>EDGE_ValidationRule_4_001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verify Osd Receivedate Less Today handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_4 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Osd Receivedate Less Today</t>
+          <t>ValidationRule_4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>POS_Pc Part Sno Mandatory_001</t>
+          <t>POS_ValidationRule_5_001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Verify Pc Part Sno Mandatory passes with valid business rule data</t>
+          <t>Verify ValidationRule_5 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pc Part Sno Mandatory</t>
+          <t>ValidationRule_5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EDGE_Pc Part Sno Mandatory_001</t>
+          <t>EDGE_ValidationRule_5_001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Verify Pc Part Sno Mandatory handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_5 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pc Part Sno Mandatory</t>
+          <t>ValidationRule_5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>POS_Preauth Expiry Date Check_001</t>
+          <t>POS_ValidationRule_6_001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Verify Preauth Expiry Date Check passes with valid business rule data</t>
+          <t>Verify ValidationRule_6 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Preauth Expiry Date Check</t>
+          <t>ValidationRule_6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EDGE_Preauth Expiry Date Check_001</t>
+          <t>EDGE_ValidationRule_6_001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Verify Preauth Expiry Date Check handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_6 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Preauth Expiry Date Check</t>
+          <t>ValidationRule_6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POS_Preauth Fulfilled Check_001</t>
+          <t>POS_ValidationRule_7_001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Verify Preauth Fulfilled Check passes with valid business rule data</t>
+          <t>Verify ValidationRule_7 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Preauth Fulfilled Check</t>
+          <t>ValidationRule_7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1400,7 +1400,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EDGE_Preauth Fulfilled Check_001</t>
+          <t>EDGE_ValidationRule_7_001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Verify Preauth Fulfilled Check handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_7 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Preauth Fulfilled Check</t>
+          <t>ValidationRule_7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1467,7 +1467,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>POS_Claim Is Locked_001</t>
+          <t>POS_ValidationRule_8_001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Verify Claim Is Locked passes with valid business rule data</t>
+          <t>Verify ValidationRule_8 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Claim Is Locked</t>
+          <t>ValidationRule_8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EDGE_Claim Is Locked_001</t>
+          <t>EDGE_ValidationRule_8_001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Verify Claim Is Locked handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_8 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Claim Is Locked</t>
+          <t>ValidationRule_8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>POS_Failure Date Validation Rule_001</t>
+          <t>POS_ValidationRule_9_001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Verify Failure Date Validation Rule passes with valid business rule data</t>
+          <t>Verify ValidationRule_9 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Failure Date Validation Rule</t>
+          <t>ValidationRule_9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EDGE_Failure Date Validation Rule_001</t>
+          <t>EDGE_ValidationRule_9_001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Verify Failure Date Validation Rule handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_9 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Failure Date Validation Rule</t>
+          <t>ValidationRule_9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1735,7 +1735,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>POS_Goodwill Type Is Missing_001</t>
+          <t>POS_ValidationRule_10_001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Verify Goodwill Type Is Missing passes with valid business rule data</t>
+          <t>Verify ValidationRule_10 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Goodwill Type Is Missing</t>
+          <t>ValidationRule_10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1802,7 +1802,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EDGE_Goodwill Type Is Missing_001</t>
+          <t>EDGE_ValidationRule_10_001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Verify Goodwill Type Is Missing handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_10 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Goodwill Type Is Missing</t>
+          <t>ValidationRule_10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1869,7 +1869,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>POS_Kbt Mc Pc Causal Mandatory_001</t>
+          <t>POS_ValidationRule_11_001</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Verify Kbt Mc Pc Causal Mandatory passes with valid business rule data</t>
+          <t>Verify ValidationRule_11 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kbt Mc Pc Causal Mandatory</t>
+          <t>ValidationRule_11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EDGE_Kbt Mc Pc Causal Mandatory_001</t>
+          <t>EDGE_ValidationRule_11_001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Verify Kbt Mc Pc Causal Mandatory handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_11 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kbt Mc Pc Causal Mandatory</t>
+          <t>ValidationRule_11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2003,7 +2003,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>POS_Kbt Mc Pc Inventory Mandatory_001</t>
+          <t>POS_ValidationRule_12_001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Verify Kbt Mc Pc Inventory Mandatory passes with valid business rule data</t>
+          <t>Verify ValidationRule_12 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kbt Mc Pc Inventory Mandatory</t>
+          <t>ValidationRule_12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2070,7 +2070,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EDGE_Kbt Mc Pc Inventory Mandatory_001</t>
+          <t>EDGE_ValidationRule_12_001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Verify Kbt Mc Pc Inventory Mandatory handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_12 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kbt Mc Pc Inventory Mandatory</t>
+          <t>ValidationRule_12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2137,7 +2137,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>POS_Incomplete Mandotory Fields_001</t>
+          <t>POS_ValidationRule_13_001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Verify Incomplete Mandotory Fields passes with valid business rule data</t>
+          <t>Verify ValidationRule_13 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Incomplete Mandotory Fields</t>
+          <t>ValidationRule_13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2204,7 +2204,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EDGE_Incomplete Mandotory Fields_001</t>
+          <t>EDGE_ValidationRule_13_001</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Verify Incomplete Mandotory Fields handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_13 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Incomplete Mandotory Fields</t>
+          <t>ValidationRule_13</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2271,7 +2271,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>POS_Kbt Pc Part Mandatory_001</t>
+          <t>POS_ValidationRule_14_001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Verify Kbt Pc Part Mandatory passes with valid business rule data</t>
+          <t>Verify ValidationRule_14 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kbt Pc Part Mandatory</t>
+          <t>ValidationRule_14</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2338,7 +2338,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EDGE_Kbt Pc Part Mandatory_001</t>
+          <t>EDGE_ValidationRule_14_001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Verify Kbt Pc Part Mandatory handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_14 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Kbt Pc Part Mandatory</t>
+          <t>ValidationRule_14</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2405,7 +2405,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>POS_Kbt Pc Purchasedate Mandatory_001</t>
+          <t>POS_ValidationRule_15_001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Verify Kbt Pc Purchasedate Mandatory passes with valid business rule data</t>
+          <t>Verify ValidationRule_15 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Kbt Pc Purchasedate Mandatory</t>
+          <t>ValidationRule_15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2472,7 +2472,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EDGE_Kbt Pc Purchasedate Mandatory_001</t>
+          <t>EDGE_ValidationRule_15_001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Verify Kbt Pc Purchasedate Mandatory handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_15 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Kbt Pc Purchasedate Mandatory</t>
+          <t>ValidationRule_15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>POS_Mc Pc Causal Claim Template Mandatory_001</t>
+          <t>POS_ValidationRule_16_001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Verify Mc Pc Causal Claim Template Mandatory passes with valid business rule data</t>
+          <t>Verify ValidationRule_16 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mc Pc Causal Claim Template Mandatory</t>
+          <t>ValidationRule_16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2606,7 +2606,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EDGE_Mc Pc Causal Claim Template Mandatory_001</t>
+          <t>EDGE_ValidationRule_16_001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Verify Mc Pc Causal Claim Template Mandatory handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_16 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mc Pc Causal Claim Template Mandatory</t>
+          <t>ValidationRule_16</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2673,7 +2673,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>POS_First Usedate Mandatory_001</t>
+          <t>POS_ValidationRule_17_001</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Verify First Usedate Mandatory passes with valid business rule data</t>
+          <t>Verify ValidationRule_17 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>First Usedate Mandatory</t>
+          <t>ValidationRule_17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2740,7 +2740,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EDGE_First Usedate Mandatory_001</t>
+          <t>EDGE_ValidationRule_17_001</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Verify First Usedate Mandatory handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_17 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>First Usedate Mandatory</t>
+          <t>ValidationRule_17</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2807,7 +2807,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>POS_Kbt Hinposeriescode Mandatory_001</t>
+          <t>POS_ValidationRule_18_001</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Verify Kbt Hinposeriescode Mandatory passes with valid business rule data</t>
+          <t>Verify ValidationRule_18 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Kbt Hinposeriescode Mandatory</t>
+          <t>ValidationRule_18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2874,7 +2874,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EDGE_Kbt Hinposeriescode Mandatory_001</t>
+          <t>EDGE_ValidationRule_18_001</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2884,12 +2884,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Verify Kbt Hinposeriescode Mandatory handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_18 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Kbt Hinposeriescode Mandatory</t>
+          <t>ValidationRule_18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>POS_Shippingcompany And Ref Num Mandatory_001</t>
+          <t>POS_ValidationRule_19_001</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Verify Shippingcompany And Ref Num Mandatory passes with valid business rule data</t>
+          <t>Verify ValidationRule_19 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Shippingcompany And Ref Num Mandatory</t>
+          <t>ValidationRule_19</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3008,7 +3008,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EDGE_Shippingcompany And Ref Num Mandatory_001</t>
+          <t>EDGE_ValidationRule_19_001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Verify Shippingcompany And Ref Num Mandatory handles boundary conditions correctly</t>
+          <t>Verify ValidationRule_19 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Shippingcompany And Ref Num Mandatory</t>
+          <t>ValidationRule_19</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3075,22 +3075,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EDL_Mc Pc Pre Auth Comments Mandatory_POS_001</t>
+          <t>POS_ValidationRule_20_001</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Mc Pc Pre Auth Comments Mandatory validation</t>
+          <t>Verify ValidationRule_20 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mc Pc Pre Auth Comments Mandatory</t>
+          <t>ValidationRule_20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3142,22 +3142,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EDL_Mc Pc Pre Auth Comments Mandatory_NEG_001</t>
+          <t>EDGE_ValidationRule_20_001</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Mc Pc Pre Auth Comments Mandatory validation</t>
+          <t>Verify ValidationRule_20 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mc Pc Pre Auth Comments Mandatory</t>
+          <t>ValidationRule_20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3209,22 +3209,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EDL_Mc Pc Pre Auth Reason Mandatory_POS_002</t>
+          <t>POS_ValidationRule_21_001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Mc Pc Pre Auth Reason Mandatory validation</t>
+          <t>Verify ValidationRule_21 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mc Pc Pre Auth Reason Mandatory</t>
+          <t>ValidationRule_21</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3276,22 +3276,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EDL_Mc Pc Pre Auth Reason Mandatory_NEG_002</t>
+          <t>EDGE_ValidationRule_21_001</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Mc Pc Pre Auth Reason Mandatory validation</t>
+          <t>Verify ValidationRule_21 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mc Pc Pre Auth Reason Mandatory</t>
+          <t>ValidationRule_21</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3343,22 +3343,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EDL_Mc Purchasedate Less Repairdate Failure_POS_003</t>
+          <t>POS_ValidationRule_22_001</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Mc Purchasedate Less Repairdate Failure validation</t>
+          <t>Verify ValidationRule_22 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mc Purchasedate Less Repairdate Failure</t>
+          <t>ValidationRule_22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3410,22 +3410,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EDL_Mc Purchasedate Less Repairdate Failure_NEG_003</t>
+          <t>EDGE_ValidationRule_22_001</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Mc Purchasedate Less Repairdate Failure validation</t>
+          <t>Verify ValidationRule_22 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mc Purchasedate Less Repairdate Failure</t>
+          <t>ValidationRule_22</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3477,22 +3477,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EDL_Osd Receivedate Less Today_POS_004</t>
+          <t>POS_ValidationRule_23_001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Osd Receivedate Less Today validation</t>
+          <t>Verify ValidationRule_23 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Osd Receivedate Less Today</t>
+          <t>ValidationRule_23</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3544,22 +3544,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EDL_Osd Receivedate Less Today_NEG_004</t>
+          <t>EDGE_ValidationRule_23_001</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Osd Receivedate Less Today validation</t>
+          <t>Verify ValidationRule_23 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Osd Receivedate Less Today</t>
+          <t>ValidationRule_23</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3611,22 +3611,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EDL_Pc Part Sno Mandatory_POS_005</t>
+          <t>POS_ValidationRule_24_001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Pc Part Sno Mandatory validation</t>
+          <t>Verify ValidationRule_24 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Pc Part Sno Mandatory</t>
+          <t>ValidationRule_24</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3678,22 +3678,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EDL_Pc Part Sno Mandatory_NEG_005</t>
+          <t>EDGE_ValidationRule_24_001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Pc Part Sno Mandatory validation</t>
+          <t>Verify ValidationRule_24 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pc Part Sno Mandatory</t>
+          <t>ValidationRule_24</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3745,22 +3745,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EDL_Preauth Expiry Date Check_POS_006</t>
+          <t>POS_ValidationRule_25_001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Preauth Expiry Date Check validation</t>
+          <t>Verify ValidationRule_25 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Preauth Expiry Date Check</t>
+          <t>ValidationRule_25</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3812,22 +3812,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EDL_Preauth Expiry Date Check_NEG_006</t>
+          <t>EDGE_ValidationRule_25_001</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Preauth Expiry Date Check validation</t>
+          <t>Verify ValidationRule_25 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Preauth Expiry Date Check</t>
+          <t>ValidationRule_25</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3879,22 +3879,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EDL_Preauth Fulfilled Check_POS_007</t>
+          <t>POS_ValidationRule_26_001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Preauth Fulfilled Check validation</t>
+          <t>Verify ValidationRule_26 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Preauth Fulfilled Check</t>
+          <t>ValidationRule_26</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3946,22 +3946,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EDL_Preauth Fulfilled Check_NEG_007</t>
+          <t>EDGE_ValidationRule_26_001</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Preauth Fulfilled Check validation</t>
+          <t>Verify ValidationRule_26 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Preauth Fulfilled Check</t>
+          <t>ValidationRule_26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4013,22 +4013,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EDL_Claim Is Locked_POS_008</t>
+          <t>POS_ValidationRule_27_001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Claim Is Locked validation</t>
+          <t>Verify ValidationRule_27 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Claim Is Locked</t>
+          <t>ValidationRule_27</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4080,22 +4080,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EDL_Claim Is Locked_NEG_008</t>
+          <t>EDGE_ValidationRule_27_001</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Claim Is Locked validation</t>
+          <t>Verify ValidationRule_27 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Claim Is Locked</t>
+          <t>ValidationRule_27</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4147,22 +4147,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EDL_Failure Date Validation Rule_POS_009</t>
+          <t>POS_ValidationRule_28_001</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Failure Date Validation Rule validation</t>
+          <t>Verify ValidationRule_28 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Failure Date Validation Rule</t>
+          <t>ValidationRule_28</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4214,22 +4214,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EDL_Failure Date Validation Rule_NEG_009</t>
+          <t>EDGE_ValidationRule_28_001</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Failure Date Validation Rule validation</t>
+          <t>Verify ValidationRule_28 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Failure Date Validation Rule</t>
+          <t>ValidationRule_28</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4281,22 +4281,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EDL_Goodwill Type Is Missing_POS_010</t>
+          <t>POS_ValidationRule_29_001</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Goodwill Type Is Missing validation</t>
+          <t>Verify ValidationRule_29 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Goodwill Type Is Missing</t>
+          <t>ValidationRule_29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4348,22 +4348,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EDL_Goodwill Type Is Missing_NEG_010</t>
+          <t>EDGE_ValidationRule_29_001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Goodwill Type Is Missing validation</t>
+          <t>Verify ValidationRule_29 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Goodwill Type Is Missing</t>
+          <t>ValidationRule_29</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4415,22 +4415,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EDL_Kbt Mc Pc Causal Mandatory_POS_011</t>
+          <t>POS_ValidationRule_30_001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Kbt Mc Pc Causal Mandatory validation</t>
+          <t>Verify ValidationRule_30 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Kbt Mc Pc Causal Mandatory</t>
+          <t>ValidationRule_30</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4482,22 +4482,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EDL_Kbt Mc Pc Causal Mandatory_NEG_011</t>
+          <t>EDGE_ValidationRule_30_001</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Kbt Mc Pc Causal Mandatory validation</t>
+          <t>Verify ValidationRule_30 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Kbt Mc Pc Causal Mandatory</t>
+          <t>ValidationRule_30</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4549,22 +4549,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EDL_Kbt Mc Pc Inventory Mandatory_POS_012</t>
+          <t>POS_ValidationRule_31_001</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Kbt Mc Pc Inventory Mandatory validation</t>
+          <t>Verify ValidationRule_31 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Kbt Mc Pc Inventory Mandatory</t>
+          <t>ValidationRule_31</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4616,22 +4616,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EDL_Kbt Mc Pc Inventory Mandatory_NEG_012</t>
+          <t>EDGE_ValidationRule_31_001</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Kbt Mc Pc Inventory Mandatory validation</t>
+          <t>Verify ValidationRule_31 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Kbt Mc Pc Inventory Mandatory</t>
+          <t>ValidationRule_31</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4683,22 +4683,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EDL_Incomplete Mandotory Fields_POS_013</t>
+          <t>POS_ValidationRule_32_001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Incomplete Mandotory Fields validation</t>
+          <t>Verify ValidationRule_32 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Incomplete Mandotory Fields</t>
+          <t>ValidationRule_32</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4750,22 +4750,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EDL_Incomplete Mandotory Fields_NEG_013</t>
+          <t>EDGE_ValidationRule_32_001</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Incomplete Mandotory Fields validation</t>
+          <t>Verify ValidationRule_32 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Incomplete Mandotory Fields</t>
+          <t>ValidationRule_32</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4817,22 +4817,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EDL_Kbt Pc Part Mandatory_POS_014</t>
+          <t>POS_ValidationRule_33_001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Kbt Pc Part Mandatory validation</t>
+          <t>Verify ValidationRule_33 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Kbt Pc Part Mandatory</t>
+          <t>ValidationRule_33</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4884,22 +4884,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EDL_Kbt Pc Part Mandatory_NEG_014</t>
+          <t>EDGE_ValidationRule_33_001</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Kbt Pc Part Mandatory validation</t>
+          <t>Verify ValidationRule_33 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Kbt Pc Part Mandatory</t>
+          <t>ValidationRule_33</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4951,22 +4951,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EDL_Kbt Pc Purchasedate Mandatory_POS_015</t>
+          <t>POS_ValidationRule_34_001</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Kbt Pc Purchasedate Mandatory validation</t>
+          <t>Verify ValidationRule_34 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Kbt Pc Purchasedate Mandatory</t>
+          <t>ValidationRule_34</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5018,22 +5018,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EDL_Kbt Pc Purchasedate Mandatory_NEG_015</t>
+          <t>EDGE_ValidationRule_34_001</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Kbt Pc Purchasedate Mandatory validation</t>
+          <t>Verify ValidationRule_34 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kbt Pc Purchasedate Mandatory</t>
+          <t>ValidationRule_34</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5085,22 +5085,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EDL_Mc Pc Causal Claim Template Mandatory_POS_016</t>
+          <t>POS_ValidationRule_35_001</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Mc Pc Causal Claim Template Mandatory validation</t>
+          <t>Verify ValidationRule_35 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mc Pc Causal Claim Template Mandatory</t>
+          <t>ValidationRule_35</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5152,22 +5152,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EDL_Mc Pc Causal Claim Template Mandatory_NEG_016</t>
+          <t>EDGE_ValidationRule_35_001</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Mc Pc Causal Claim Template Mandatory validation</t>
+          <t>Verify ValidationRule_35 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mc Pc Causal Claim Template Mandatory</t>
+          <t>ValidationRule_35</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5219,22 +5219,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EDL_First Usedate Mandatory_POS_017</t>
+          <t>POS_ValidationRule_36_001</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Load valid data that should pass First Usedate Mandatory validation</t>
+          <t>Verify ValidationRule_36 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>First Usedate Mandatory</t>
+          <t>ValidationRule_36</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5286,22 +5286,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EDL_First Usedate Mandatory_NEG_017</t>
+          <t>EDGE_ValidationRule_36_001</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail First Usedate Mandatory validation</t>
+          <t>Verify ValidationRule_36 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>First Usedate Mandatory</t>
+          <t>ValidationRule_36</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5353,22 +5353,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EDL_Kbt Hinposeriescode Mandatory_POS_018</t>
+          <t>POS_ValidationRule_37_001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Kbt Hinposeriescode Mandatory validation</t>
+          <t>Verify ValidationRule_37 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Kbt Hinposeriescode Mandatory</t>
+          <t>ValidationRule_37</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5420,22 +5420,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EDL_Kbt Hinposeriescode Mandatory_NEG_018</t>
+          <t>EDGE_ValidationRule_37_001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Edge Case Testing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Attempt to load invalid data that should fail Kbt Hinposeriescode Mandatory validation</t>
+          <t>Verify ValidationRule_37 handles boundary conditions correctly</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kbt Hinposeriescode Mandatory</t>
+          <t>ValidationRule_37</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEPENDS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5487,22 +5487,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EDL_Shippingcompany And Ref Num Mandatory_POS_019</t>
+          <t>POS_ValidationRule_38_001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Enhanced Data Loading</t>
+          <t>Positive Validation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Load valid data that should pass Shippingcompany And Ref Num Mandatory validation</t>
+          <t>Verify ValidationRule_38 passes with valid business rule data</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Shippingcompany And Ref Num Mandatory</t>
+          <t>ValidationRule_38</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5554,65 +5554,2745 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EDL_Shippingcompany And Ref Num Mandatory_NEG_019</t>
+          <t>EDGE_ValidationRule_38_001</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>Edge Case Testing</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Verify ValidationRule_38 handles boundary conditions correctly</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ValidationRule_38</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>DEPENDS</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_1_POS_001</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>Enhanced Data Loading</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Attempt to load invalid data that should fail Shippingcompany And Ref Num Mandatory validation</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Shippingcompany And Ref Num Mandatory</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>General Business Rule</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_1 validation</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ValidationRule_1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>genai_driven</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_1_NEG_001</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_1 validation</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ValidationRule_1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_2_POS_002</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_2 validation</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ValidationRule_2</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_2_NEG_002</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_2 validation</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ValidationRule_2</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_3_POS_003</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_3 validation</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ValidationRule_3</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_3_NEG_003</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_3 validation</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ValidationRule_3</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_4_POS_004</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_4 validation</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ValidationRule_4</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_4_NEG_004</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_4 validation</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ValidationRule_4</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_5_POS_005</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_5 validation</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ValidationRule_5</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_5_NEG_005</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_5 validation</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ValidationRule_5</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_6_POS_006</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_6 validation</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ValidationRule_6</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_6_NEG_006</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_6 validation</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ValidationRule_6</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_7_POS_007</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_7 validation</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ValidationRule_7</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_7_NEG_007</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_7 validation</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ValidationRule_7</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_8_POS_008</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_8 validation</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ValidationRule_8</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_8_NEG_008</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_8 validation</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ValidationRule_8</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_9_POS_009</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_9 validation</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ValidationRule_9</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_9_NEG_009</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_9 validation</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ValidationRule_9</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_10_POS_010</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_10 validation</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ValidationRule_10</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_10_NEG_010</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_10 validation</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ValidationRule_10</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_11_POS_011</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_11 validation</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ValidationRule_11</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_11_NEG_011</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_11 validation</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ValidationRule_11</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_12_POS_012</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_12 validation</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ValidationRule_12</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_12_NEG_012</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_12 validation</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ValidationRule_12</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_13_POS_013</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_13 validation</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ValidationRule_13</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_13_NEG_013</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_13 validation</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ValidationRule_13</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_14_POS_014</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_14 validation</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ValidationRule_14</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_14_NEG_014</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_14 validation</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ValidationRule_14</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_15_POS_015</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_15 validation</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ValidationRule_15</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_15_NEG_015</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_15 validation</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ValidationRule_15</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_16_POS_016</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_16 validation</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ValidationRule_16</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_16_NEG_016</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_16 validation</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ValidationRule_16</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_17_POS_017</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_17 validation</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ValidationRule_17</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_17_NEG_017</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_17 validation</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ValidationRule_17</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_18_POS_018</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_18 validation</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ValidationRule_18</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_18_NEG_018</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_18 validation</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ValidationRule_18</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_19_POS_019</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_19 validation</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ValidationRule_19</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_19_NEG_019</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_19 validation</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ValidationRule_19</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_20_POS_020</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Load valid data that should pass ValidationRule_20 validation</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ValidationRule_20</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>EDL_ValidationRule_20_NEG_020</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Enhanced Data Loading</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Attempt to load invalid data that should fail ValidationRule_20 validation</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ValidationRule_20</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>genai_driven</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5629,10 +8309,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
@@ -5669,7 +8349,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mc Pc Pre Auth Comments Mandatory</t>
+          <t>ValidationRule_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5684,7 +8364,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Machine, Permission, Part, WOD_2__SkipTriggerNValidations, WOD_2__Pre_Authorization_Comments__c, WOD_2__DisableSkipTriggerNValidation, WOD_2__Is_Pre_Authorization_Required__c, WOD_2__Claim_Type__c</t>
+          <t>WOD_2__Pre_Authorization_Comments__c, Part, WOD_2__Claim_Type__c, WOD_2__DisableSkipTriggerNValidation, Permission, WOD_2__Is_Pre_Authorization_Required__c, Machine, WOD_2__SkipTriggerNValidations</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5696,7 +8376,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mc Pc Pre Auth Reason Mandatory</t>
+          <t>ValidationRule_2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5709,11 +8389,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -5723,7 +8399,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mc Purchasedate Less Repairdate Failure</t>
+          <t>ValidationRule_3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5750,7 +8426,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Osd Receivedate Less Today</t>
+          <t>ValidationRule_4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5763,11 +8439,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -5777,7 +8449,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pc Part Sno Mandatory</t>
+          <t>ValidationRule_5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5787,12 +8459,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WOD_2__Is_Serialized__c, Permission, Part, WOD_2__SkipTriggerNValidations, WOD_2__Part_Serial_Number__c, WOD_2__DisableSkipTriggerNValidation, WOD_2__PartNumber_P2__r, WOD_2__Track_Type__c, Serialized, WOD_2__Claim_Type__c, WOD_2__Part__r</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5804,7 +8476,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Preauth Expiry Date Check</t>
+          <t>ValidationRule_6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5817,11 +8489,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -5831,7 +8499,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Preauth Fulfilled Check</t>
+          <t>ValidationRule_7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5858,7 +8526,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Claim Is Locked</t>
+          <t>ValidationRule_8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5871,11 +8539,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -5885,7 +8549,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Failure Date Validation Rule</t>
+          <t>ValidationRule_9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5895,12 +8559,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>Part, WOD_2__Claim_Type__c, WOD_2__PartNumber_P2__r, WOD_2__DisableSkipTriggerNValidation, Serialized, Permission, WOD_2__Part__r, WOD_2__Part_Serial_Number__c, WOD_2__Is_Serialized__c, WOD_2__Track_Type__c, WOD_2__SkipTriggerNValidations</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5912,7 +8576,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Goodwill Type Is Missing</t>
+          <t>ValidationRule_10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5925,11 +8589,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -5939,7 +8599,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kbt Mc Pc Causal Mandatory</t>
+          <t>ValidationRule_11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5949,12 +8609,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Claim, Modification, Machine, WOD_2__Claim_Status__c, RBOX, Part, Initial, Draft, Template, Field, WOD_2__Causal_Part_Number__c, WOD_2__Claim_Type__c, KBT_Claim_Source_System__c</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5966,7 +8626,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kbt Mc Pc Inventory Mandatory</t>
+          <t>ValidationRule_12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5976,14 +8636,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>WOD_2__Inventory__c, WOD_2__Claim_Status__c, Machine, OEM, Part, Initial, Draft, machine, on, WOD_2__Host_NonHost__c, WOD_2__Claim_Type__c, Installed</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -5993,7 +8649,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Incomplete Mandotory Fields</t>
+          <t>ValidationRule_13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6003,12 +8659,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>null, WOD_2__Account__c, Claim, Template, WOD_2__Date_Of_Repair__c, WOD_2__Claim_Type__c, WOD_2__Date_Of_Failure__c</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6020,7 +8676,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kbt Pc Part Mandatory</t>
+          <t>ValidationRule_14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6030,14 +8686,10 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>WOD_2__Part__c, WOD_2__Claim_Status__c, RBOX, Part, Initial, Draft, WOD_2__Claim_Type__c, KBT_Claim_Source_System__c</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -6047,7 +8699,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kbt Pc Purchasedate Mandatory</t>
+          <t>ValidationRule_15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6057,12 +8709,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WOD_2__Claim_Status__c, RBOX, Part, Initial, WOD_2__Date_Of_Purchase__c, Draft, WOD_2__Claim_Type__c, KBT_Claim_Source_System__c</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6074,7 +8726,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mc Pc Causal Claim Template Mandatory</t>
+          <t>ValidationRule_16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6084,14 +8736,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Claim, Permission, WOD_2__SkipTriggerNValidations, WOD_2__DisableSkipTriggerNValidation, Template, WOD_2__CausalPartNumber_P2__c, WOD_2__Causal_Part_Number__c, WOD_2__Claim_Type__c</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -6101,7 +8749,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>First Usedate Mandatory</t>
+          <t>ValidationRule_17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6116,7 +8764,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KBT_FirstUseDate__c, KBT_Inventory_Type__c, Retail</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6128,7 +8776,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kbt Hinposeriescode Mandatory</t>
+          <t>ValidationRule_18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6138,14 +8786,10 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>WOD_2__Parent_Product__c, KBT_Reference_tracking_number__c, KBT_Shipping_Company__c, WOD_2__Item__c, WOD_2__Parent_Product__r, WOD_2__Item__r, KBT_HinpoSeriesCode__c, WOD_2__Inventory__r</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>General Business Rule</t>
@@ -6155,7 +8799,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shippingcompany And Ref Num Mandatory</t>
+          <t>ValidationRule_19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6165,15 +8809,488 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ValidationRule_20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ValidationRule_21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>KBT_Reference_tracking_number__c, KBT_Shipping_Company__c, WOD_2__Claim_Status__c, Initial, KBT_Hinpo_Code__c, Draft</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Initial, Field, Part, WOD_2__Claim_Status__c, WOD_2__Claim_Type__c, Modification, Draft, Claim, Machine, KBT_Claim_Source_System__c, Template, RBOX, WOD_2__Causal_Part_Number__c</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ValidationRule_22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ValidationRule_23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Initial, machine, Part, WOD_2__Claim_Status__c, WOD_2__Inventory__c, WOD_2__Claim_Type__c, Draft, Installed, OEM, Machine, on, WOD_2__Host_NonHost__c</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ValidationRule_24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ValidationRule_25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>WOD_2__Account__c, null, WOD_2__Claim_Type__c, WOD_2__Date_Of_Repair__c, Claim, WOD_2__Date_Of_Failure__c, Template</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ValidationRule_26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ValidationRule_27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Initial, Part, WOD_2__Claim_Status__c, WOD_2__Claim_Type__c, Draft, KBT_Claim_Source_System__c, RBOX, WOD_2__Part__c</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ValidationRule_28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ValidationRule_29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Initial, Part, WOD_2__Claim_Status__c, WOD_2__Claim_Type__c, Draft, WOD_2__Date_Of_Purchase__c, KBT_Claim_Source_System__c, RBOX</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ValidationRule_30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ValidationRule_31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>WOD_2__Claim_Type__c, WOD_2__DisableSkipTriggerNValidation, Permission, Claim, Template, WOD_2__SkipTriggerNValidations, WOD_2__CausalPartNumber_P2__c, WOD_2__Causal_Part_Number__c</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ValidationRule_32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ValidationRule_33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Retail, KBT_FirstUseDate__c, KBT_Inventory_Type__c</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ValidationRule_34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ValidationRule_35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>WOD_2__Parent_Product__c, KBT_Reference_tracking_number__c, WOD_2__Item__r, KBT_Shipping_Company__c, WOD_2__Item__c, KBT_HinpoSeriesCode__c, WOD_2__Parent_Product__r, WOD_2__Inventory__r</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ValidationRule_36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ValidationRule_37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Initial, KBT_Hinpo_Code__c, KBT_Reference_tracking_number__c, WOD_2__Claim_Status__c, KBT_Shipping_Company__c, Draft</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>General Business Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ValidationRule_38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>formula_validation</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
         <is>
           <t>General Business Rule</t>
         </is>
@@ -6274,7 +9391,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6291,7 +9408,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6359,7 +9476,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6410,7 +9527,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6456,7 +9573,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3">
